--- a/config/lines/撒粉复合机.xlsx
+++ b/config/lines/撒粉复合机.xlsx
@@ -11,6 +11,7 @@
     <x:sheet name="字段映射" sheetId="3" r:id="rId4"/>
     <x:sheet name="点表" sheetId="4" r:id="rId5"/>
     <x:sheet name="显示分组说明" sheetId="5" r:id="rId6"/>
+    <x:sheet name="MQTT目标" sheetId="6" r:id="rId9"/>
   </x:sheets>
   <x:definedNames/>
   <x:calcPr calcId="125725"/>
@@ -329,42 +330,81 @@
     <x:t>运行状态</x:t>
   </x:si>
   <x:si>
+    <x:t>sfxh</x:t>
+  </x:si>
+  <x:si>
     <x:t>撒粉型号</x:t>
   </x:si>
   <x:si>
+    <x:t>sfl</x:t>
+  </x:si>
+  <x:si>
     <x:t>撒粉量</x:t>
   </x:si>
   <x:si>
+    <x:t>hxwd1</x:t>
+  </x:si>
+  <x:si>
     <x:t>烘箱温度1</x:t>
   </x:si>
   <x:si>
+    <x:t>hxwd2</x:t>
+  </x:si>
+  <x:si>
     <x:t>烘箱温度2</x:t>
   </x:si>
   <x:si>
+    <x:t>zgtwd</x:t>
+  </x:si>
+  <x:si>
     <x:t>主辊筒温度</x:t>
   </x:si>
   <x:si>
+    <x:t>zgtcs</x:t>
+  </x:si>
+  <x:si>
     <x:t>主辊筒车速</x:t>
   </x:si>
   <x:si>
+    <x:t>syg1</x:t>
+  </x:si>
+  <x:si>
     <x:t>上压辊1（闭合/打开）</x:t>
   </x:si>
   <x:si>
+    <x:t>syg1jx</x:t>
+  </x:si>
+  <x:si>
     <x:t>上压辊1间隙</x:t>
   </x:si>
   <x:si>
+    <x:t>xyg2</x:t>
+  </x:si>
+  <x:si>
     <x:t>下压辊2（闭合/打开）</x:t>
   </x:si>
   <x:si>
+    <x:t>xyg2jx</x:t>
+  </x:si>
+  <x:si>
     <x:t>下压辊2间隙</x:t>
   </x:si>
   <x:si>
+    <x:t>qdjj</x:t>
+  </x:si>
+  <x:si>
     <x:t>切刀间距</x:t>
   </x:si>
   <x:si>
+    <x:t>mf</x:t>
+  </x:si>
+  <x:si>
     <x:t>门幅</x:t>
   </x:si>
   <x:si>
+    <x:t>hd</x:t>
+  </x:si>
+  <x:si>
     <x:t>厚度</x:t>
   </x:si>
   <x:si>
@@ -524,43 +564,37 @@
     <x:t>在「点表」工作表的「显示分组」列填写上表分组名称；留空则程序按数据类型自动推断。</x:t>
   </x:si>
   <x:si>
-    <x:t>sfxh</x:t>
-  </x:si>
-  <x:si>
-    <x:t>sfl</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hxwd1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hxwd2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zgtwd</x:t>
-  </x:si>
-  <x:si>
-    <x:t>zgtcs</x:t>
-  </x:si>
-  <x:si>
-    <x:t>syg1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>syg1jx</x:t>
-  </x:si>
-  <x:si>
-    <x:t>xyg2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>xyg2jx</x:t>
-  </x:si>
-  <x:si>
-    <x:t>qdjj</x:t>
-  </x:si>
-  <x:si>
-    <x:t>mf</x:t>
-  </x:si>
-  <x:si>
-    <x:t>hd</x:t>
+    <x:t>Broker</x:t>
+  </x:si>
+  <x:si>
+    <x:t>端口</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ClientId</x:t>
+  </x:si>
+  <x:si>
+    <x:t>用户名</x:t>
+  </x:si>
+  <x:si>
+    <x:t>密码</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TLS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QoS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>主题</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>默认</x:t>
+  </x:si>
+  <x:si>
+    <x:t>971f886043aa4ebcbc47484352c3cfdc</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1413,106 +1447,106 @@
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>106</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="0" t="s">
-        <x:v>171</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>110</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:2">
       <x:c r="A7" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>112</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:2">
       <x:c r="A8" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:2">
       <x:c r="A9" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:2">
       <x:c r="A10" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>118</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:2">
       <x:c r="A11" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>120</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:2">
       <x:c r="A12" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:2">
       <x:c r="A13" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:2">
       <x:c r="A14" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:2">
       <x:c r="A15" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -1546,43 +1580,43 @@
   <x:sheetData>
     <x:row r="1" spans="1:13" s="1" customFormat="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="H1" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="I1" s="1" t="s">
         <x:v>35</x:v>
       </x:c>
       <x:c r="J1" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="K1" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="L1" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="M1" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>140</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:13">
@@ -1590,19 +1624,19 @@
         <x:v>102</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s">
         <x:v>38</x:v>
@@ -1620,7 +1654,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L2" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="M2" s="0" t="s">
         <x:v>56</x:v>
@@ -1628,22 +1662,22 @@
     </x:row>
     <x:row r="3" spans="1:13">
       <x:c r="A3" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s">
         <x:v>38</x:v>
@@ -1661,7 +1695,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L3" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="M3" s="0" t="s">
         <x:v>56</x:v>
@@ -1669,22 +1703,22 @@
     </x:row>
     <x:row r="4" spans="1:13">
       <x:c r="A4" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s">
         <x:v>38</x:v>
@@ -1702,7 +1736,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L4" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="M4" s="0" t="s">
         <x:v>56</x:v>
@@ -1710,22 +1744,22 @@
     </x:row>
     <x:row r="5" spans="1:13">
       <x:c r="A5" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
         <x:v>38</x:v>
@@ -1743,7 +1777,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
         <x:v>56</x:v>
@@ -1751,22 +1785,22 @@
     </x:row>
     <x:row r="6" spans="1:13">
       <x:c r="A6" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
         <x:v>38</x:v>
@@ -1784,7 +1818,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L6" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="M6" s="0" t="s">
         <x:v>56</x:v>
@@ -1792,22 +1826,22 @@
     </x:row>
     <x:row r="7" spans="1:13">
       <x:c r="A7" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G7" s="0" t="s">
         <x:v>38</x:v>
@@ -1825,7 +1859,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L7" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="M7" s="0" t="s">
         <x:v>56</x:v>
@@ -1833,22 +1867,22 @@
     </x:row>
     <x:row r="8" spans="1:13">
       <x:c r="A8" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G8" s="0" t="s">
         <x:v>38</x:v>
@@ -1866,7 +1900,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L8" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="M8" s="0" t="s">
         <x:v>56</x:v>
@@ -1874,22 +1908,22 @@
     </x:row>
     <x:row r="9" spans="1:13">
       <x:c r="A9" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="D9" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="E9" s="0" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="F9" s="0" t="s">
         <x:v>144</x:v>
-      </x:c>
-      <x:c r="D9" s="0" t="s">
-        <x:v>136</x:v>
-      </x:c>
-      <x:c r="E9" s="0" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="F9" s="0" t="s">
-        <x:v>131</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
         <x:v>38</x:v>
@@ -1907,7 +1941,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="M9" s="0" t="s">
         <x:v>56</x:v>
@@ -1915,22 +1949,22 @@
     </x:row>
     <x:row r="10" spans="1:13">
       <x:c r="A10" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G10" s="0" t="s">
         <x:v>38</x:v>
@@ -1948,7 +1982,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L10" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="M10" s="0" t="s">
         <x:v>56</x:v>
@@ -1956,22 +1990,22 @@
     </x:row>
     <x:row r="11" spans="1:13">
       <x:c r="A11" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
         <x:v>38</x:v>
@@ -1989,7 +2023,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L11" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="M11" s="0" t="s">
         <x:v>56</x:v>
@@ -1997,22 +2031,22 @@
     </x:row>
     <x:row r="12" spans="1:13">
       <x:c r="A12" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G12" s="0" t="s">
         <x:v>38</x:v>
@@ -2030,7 +2064,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L12" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="M12" s="0" t="s">
         <x:v>56</x:v>
@@ -2038,22 +2072,22 @@
     </x:row>
     <x:row r="13" spans="1:13">
       <x:c r="A13" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
         <x:v>38</x:v>
@@ -2071,7 +2105,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L13" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="M13" s="0" t="s">
         <x:v>56</x:v>
@@ -2079,22 +2113,22 @@
     </x:row>
     <x:row r="14" spans="1:13">
       <x:c r="A14" s="0" t="s">
-        <x:v>114</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G14" s="0" t="s">
         <x:v>38</x:v>
@@ -2112,7 +2146,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L14" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="M14" s="0" t="s">
         <x:v>56</x:v>
@@ -2120,22 +2154,22 @@
     </x:row>
     <x:row r="15" spans="1:13">
       <x:c r="A15" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
         <x:v>84</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
         <x:v>38</x:v>
@@ -2153,7 +2187,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L15" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="M15" s="0" t="s">
         <x:v>56</x:v>
@@ -2184,96 +2218,195 @@
   <x:sheetData>
     <x:row r="1" spans="1:4" s="1" customFormat="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>149</x:v>
+        <x:v>162</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="0" t="s">
-        <x:v>132</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>165</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>168</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>171</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>174</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>178</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>179</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="0" t="s">
-        <x:v>167</x:v>
+        <x:v>180</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
+  <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
+  <x:headerFooter/>
+  <x:tableParts count="0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x14ac">
+  <x:sheetPr>
+    <x:outlinePr summaryBelow="1" summaryRight="1"/>
+  </x:sheetPr>
+  <x:dimension ref="A1:K2"/>
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="2" width="2.996339" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="13.282054" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="4.996339" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="7.853482" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="6.424911" style="0" customWidth="1"/>
+    <x:col min="7" max="7" width="11.853482" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="3.853482" style="0" customWidth="1"/>
+    <x:col min="9" max="9" width="4.567768" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="31.139196" style="0" customWidth="1"/>
+    <x:col min="11" max="11" width="33.567768" style="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" spans="1:11" s="1" customFormat="1">
+      <x:c r="A1" s="1" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="B1" s="1" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="C1" s="1" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="D1" s="1" t="s">
+        <x:v>182</x:v>
+      </x:c>
+      <x:c r="E1" s="1" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="G1" s="1" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="H1" s="1" t="s">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="I1" s="1" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="J1" s="1" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="K1" s="1" t="s">
+        <x:v>189</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:11">
+      <x:c r="A2" s="0" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C2" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="D2" s="0">
+        <x:v>1888</x:v>
+      </x:c>
+      <x:c r="E2" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="F2" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="H2" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="I2" s="0">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J2" s="0" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="K2" s="0" t="s">
+        <x:v>191</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/config/lines/撒粉复合机.xlsx
+++ b/config/lines/撒粉复合机.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="190">
   <si>
     <t>配置项</t>
   </si>
@@ -153,102 +153,102 @@
     <t>使用模拟数据</t>
   </si>
   <si>
+    <t>否</t>
+  </si>
+  <si>
+    <t>UseSimulator</t>
+  </si>
+  <si>
+    <t>MQTT_Broker</t>
+  </si>
+  <si>
+    <t>192.168.16.18</t>
+  </si>
+  <si>
+    <t>MqttHost</t>
+  </si>
+  <si>
+    <t>MQTT端口</t>
+  </si>
+  <si>
+    <t>1888</t>
+  </si>
+  <si>
+    <t>MqttPort</t>
+  </si>
+  <si>
+    <t>MQTT_ClientId</t>
+  </si>
+  <si>
+    <t>SFHFJ</t>
+  </si>
+  <si>
+    <t>MqttClientId</t>
+  </si>
+  <si>
+    <t>MQTT_用户名</t>
+  </si>
+  <si>
+    <t>hg_iot</t>
+  </si>
+  <si>
+    <t>MqttUsername</t>
+  </si>
+  <si>
+    <t>MQTT_密码</t>
+  </si>
+  <si>
+    <t>Hg@Iot2026</t>
+  </si>
+  <si>
+    <t>MqttPassword</t>
+  </si>
+  <si>
+    <t>MQTT_TLS</t>
+  </si>
+  <si>
+    <t>MqttUseTls</t>
+  </si>
+  <si>
+    <t>MQTT_QoS</t>
+  </si>
+  <si>
+    <t>MqttQos</t>
+  </si>
+  <si>
+    <t>MQTT发布主题</t>
+  </si>
+  <si>
+    <t>/RRJFHJ/SFHFJ/properties/report</t>
+  </si>
+  <si>
+    <t>MqttTopic</t>
+  </si>
+  <si>
+    <t>订阅主题</t>
+  </si>
+  <si>
+    <t>/RRJFHJ/XHRRJFHJ/properties/report;/RRJFHJ/HDRRJFHJ/properties/report</t>
+  </si>
+  <si>
+    <t>SubscribeTopics</t>
+  </si>
+  <si>
+    <t>运行模式</t>
+  </si>
+  <si>
+    <t>采集模式</t>
+  </si>
+  <si>
+    <t>OperationMode</t>
+  </si>
+  <si>
+    <t>开机自动启动</t>
+  </si>
+  <si>
     <t>是</t>
   </si>
   <si>
-    <t>UseSimulator</t>
-  </si>
-  <si>
-    <t>MQTT_Broker</t>
-  </si>
-  <si>
-    <t>192.168.16.18</t>
-  </si>
-  <si>
-    <t>MqttHost</t>
-  </si>
-  <si>
-    <t>MQTT端口</t>
-  </si>
-  <si>
-    <t>1888</t>
-  </si>
-  <si>
-    <t>MqttPort</t>
-  </si>
-  <si>
-    <t>MQTT_ClientId</t>
-  </si>
-  <si>
-    <t>SFHFJ</t>
-  </si>
-  <si>
-    <t>MqttClientId</t>
-  </si>
-  <si>
-    <t>MQTT_用户名</t>
-  </si>
-  <si>
-    <t>hg_iot</t>
-  </si>
-  <si>
-    <t>MqttUsername</t>
-  </si>
-  <si>
-    <t>MQTT_密码</t>
-  </si>
-  <si>
-    <t>Hg@Iot2026</t>
-  </si>
-  <si>
-    <t>MqttPassword</t>
-  </si>
-  <si>
-    <t>MQTT_TLS</t>
-  </si>
-  <si>
-    <t>否</t>
-  </si>
-  <si>
-    <t>MqttUseTls</t>
-  </si>
-  <si>
-    <t>MQTT_QoS</t>
-  </si>
-  <si>
-    <t>MqttQos</t>
-  </si>
-  <si>
-    <t>MQTT发布主题</t>
-  </si>
-  <si>
-    <t>/RRJFHJ/SFHFJ/properties/report</t>
-  </si>
-  <si>
-    <t>MqttTopic</t>
-  </si>
-  <si>
-    <t>订阅主题</t>
-  </si>
-  <si>
-    <t>/RRJFHJ/XHRRJFHJ/properties/report;/RRJFHJ/HDRRJFHJ/properties/report</t>
-  </si>
-  <si>
-    <t>SubscribeTopics</t>
-  </si>
-  <si>
-    <t>运行模式</t>
-  </si>
-  <si>
-    <t>采集模式</t>
-  </si>
-  <si>
-    <t>OperationMode</t>
-  </si>
-  <si>
-    <t>开机自动启动</t>
-  </si>
-  <si>
     <t>StartWithWindows</t>
   </si>
   <si>
@@ -390,7 +390,27 @@
     <t>syg1jx</t>
   </si>
   <si>
-    <t>上压辊1间隙</t>
+    <r>
+      <t>上压辊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>间隙</t>
+    </r>
   </si>
   <si>
     <t>xyg2</t>
@@ -402,7 +422,27 @@
     <t>xyg2jx</t>
   </si>
   <si>
-    <t>下压辊2间隙</t>
+    <r>
+      <t>下压辊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>间隙</t>
+    </r>
   </si>
   <si>
     <t>qdjj</t>
@@ -505,6 +545,47 @@
   </si>
   <si>
     <t>工艺参数</t>
+  </si>
+  <si>
+    <r>
+      <t>上压辊</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（闭合</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <charset val="134"/>
+      </rPr>
+      <t>/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>打开）</t>
+    </r>
   </si>
   <si>
     <t>D1040</t>
@@ -1955,7 +2036,7 @@
       <c r="A14" t="s">
         <v>37</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="2" t="s">
         <v>38</v>
       </c>
       <c r="C14" t="s">
@@ -2022,62 +2103,62 @@
         <v>55</v>
       </c>
       <c r="B20" t="s">
+        <v>38</v>
+      </c>
+      <c r="C20" t="s">
         <v>56</v>
-      </c>
-      <c r="C20" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:3">
       <c r="A21" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B21" t="s">
         <v>33</v>
       </c>
       <c r="C21" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
+        <v>59</v>
+      </c>
+      <c r="B22" t="s">
         <v>60</v>
       </c>
-      <c r="B22" t="s">
+      <c r="C22" t="s">
         <v>61</v>
-      </c>
-      <c r="C22" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" t="s">
         <v>63</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>64</v>
-      </c>
-      <c r="C23" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24" t="s">
         <v>66</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>67</v>
-      </c>
-      <c r="C24" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
+        <v>68</v>
+      </c>
+      <c r="B25" t="s">
         <v>69</v>
-      </c>
-      <c r="B25" t="s">
-        <v>38</v>
       </c>
       <c r="C25" t="s">
         <v>70</v>
@@ -2088,7 +2169,7 @@
         <v>71</v>
       </c>
       <c r="B26" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="C26" t="s">
         <v>72</v>
@@ -2099,7 +2180,7 @@
         <v>73</v>
       </c>
       <c r="B27" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="C27" t="s">
         <v>74</v>
@@ -2238,7 +2319,7 @@
         <v>96</v>
       </c>
       <c r="B10" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="C10" t="s">
         <v>97</v>
@@ -2337,7 +2418,7 @@
       <c r="A10" t="s">
         <v>116</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="2" t="s">
         <v>117</v>
       </c>
     </row>
@@ -2353,7 +2434,7 @@
       <c r="A12" t="s">
         <v>120</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
         <v>121</v>
       </c>
     </row>
@@ -2391,10 +2472,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="18.2857142857143" customWidth="1"/>
+    <col min="1" max="1" width="46.7142857142857" customWidth="1"/>
     <col min="2" max="2" width="15" customWidth="1"/>
     <col min="3" max="3" width="6.28571428571429" customWidth="1"/>
     <col min="4" max="4" width="7.57142857142857" customWidth="1"/>
@@ -2467,7 +2548,7 @@
         <v>143</v>
       </c>
       <c r="G2" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="H2" t="s">
         <v>83</v>
@@ -2485,7 +2566,7 @@
         <v>144</v>
       </c>
       <c r="M2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:13">
@@ -2508,7 +2589,7 @@
         <v>143</v>
       </c>
       <c r="G3" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="H3" t="s">
         <v>83</v>
@@ -2526,7 +2607,7 @@
         <v>147</v>
       </c>
       <c r="M3" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -2549,7 +2630,7 @@
         <v>143</v>
       </c>
       <c r="G4" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="H4" t="s">
         <v>83</v>
@@ -2567,7 +2648,7 @@
         <v>147</v>
       </c>
       <c r="M4" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:13">
@@ -2590,7 +2671,7 @@
         <v>143</v>
       </c>
       <c r="G5" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="H5" t="s">
         <v>83</v>
@@ -2608,7 +2689,7 @@
         <v>151</v>
       </c>
       <c r="M5" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2631,7 +2712,7 @@
         <v>143</v>
       </c>
       <c r="G6" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="H6" t="s">
         <v>83</v>
@@ -2649,7 +2730,7 @@
         <v>151</v>
       </c>
       <c r="M6" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:13">
@@ -2672,7 +2753,7 @@
         <v>143</v>
       </c>
       <c r="G7" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="H7" t="s">
         <v>83</v>
@@ -2690,7 +2771,7 @@
         <v>151</v>
       </c>
       <c r="M7" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:13">
@@ -2713,7 +2794,7 @@
         <v>143</v>
       </c>
       <c r="G8" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="H8" t="s">
         <v>83</v>
@@ -2731,18 +2812,18 @@
         <v>155</v>
       </c>
       <c r="M8" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" t="s">
-        <v>115</v>
-      </c>
-      <c r="B9" t="s">
-        <v>140</v>
+      <c r="A9" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>145</v>
       </c>
       <c r="C9" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="D9" t="s">
         <v>148</v>
@@ -2754,7 +2835,7 @@
         <v>143</v>
       </c>
       <c r="G9" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="H9" t="s">
         <v>83</v>
@@ -2772,18 +2853,18 @@
         <v>155</v>
       </c>
       <c r="M9" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="s">
         <v>119</v>
       </c>
-      <c r="B10" t="s">
-        <v>140</v>
+      <c r="B10" s="2" t="s">
+        <v>145</v>
       </c>
       <c r="C10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D10" t="s">
         <v>148</v>
@@ -2795,7 +2876,7 @@
         <v>143</v>
       </c>
       <c r="G10" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="H10" t="s">
         <v>83</v>
@@ -2813,7 +2894,7 @@
         <v>155</v>
       </c>
       <c r="M10" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:13">
@@ -2836,7 +2917,7 @@
         <v>143</v>
       </c>
       <c r="G11" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="H11" t="s">
         <v>83</v>
@@ -2854,7 +2935,7 @@
         <v>147</v>
       </c>
       <c r="M11" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
     </row>
     <row r="12" spans="1:13">
@@ -2877,7 +2958,7 @@
         <v>143</v>
       </c>
       <c r="G12" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="H12" t="s">
         <v>83</v>
@@ -2895,14 +2976,14 @@
         <v>147</v>
       </c>
       <c r="M12" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" t="s">
         <v>127</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="2" t="s">
         <v>145</v>
       </c>
       <c r="C13" t="s">
@@ -2918,7 +2999,7 @@
         <v>143</v>
       </c>
       <c r="G13" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="H13" t="s">
         <v>83</v>
@@ -2936,7 +3017,89 @@
         <v>147</v>
       </c>
       <c r="M13" t="s">
-        <v>56</v>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C14" t="s">
+        <v>83</v>
+      </c>
+      <c r="D14" t="s">
+        <v>148</v>
+      </c>
+      <c r="E14" t="s">
+        <v>83</v>
+      </c>
+      <c r="F14" t="s">
+        <v>143</v>
+      </c>
+      <c r="G14" t="s">
+        <v>69</v>
+      </c>
+      <c r="H14" t="s">
+        <v>83</v>
+      </c>
+      <c r="I14" t="s">
+        <v>83</v>
+      </c>
+      <c r="J14">
+        <v>1</v>
+      </c>
+      <c r="K14">
+        <v>0</v>
+      </c>
+      <c r="L14" t="s">
+        <v>147</v>
+      </c>
+      <c r="M14" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C15" t="s">
+        <v>83</v>
+      </c>
+      <c r="D15" t="s">
+        <v>148</v>
+      </c>
+      <c r="E15" t="s">
+        <v>83</v>
+      </c>
+      <c r="F15" t="s">
+        <v>143</v>
+      </c>
+      <c r="G15" t="s">
+        <v>69</v>
+      </c>
+      <c r="H15" t="s">
+        <v>83</v>
+      </c>
+      <c r="I15" t="s">
+        <v>83</v>
+      </c>
+      <c r="J15">
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <v>0</v>
+      </c>
+      <c r="L15" t="s">
+        <v>147</v>
+      </c>
+      <c r="M15" t="s">
+        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -2966,10 +3129,10 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -2977,13 +3140,13 @@
         <v>144</v>
       </c>
       <c r="B2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2991,13 +3154,13 @@
         <v>151</v>
       </c>
       <c r="B3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -3005,13 +3168,13 @@
         <v>155</v>
       </c>
       <c r="B4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3019,37 +3182,37 @@
         <v>147</v>
       </c>
       <c r="B5" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C5" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="D5" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="D6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -3085,39 +3248,39 @@
         <v>134</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B2" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="C2" t="s">
         <v>41</v>
@@ -3135,16 +3298,16 @@
         <v>53</v>
       </c>
       <c r="H2" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="K2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
   </sheetData>

--- a/config/lines/撒粉复合机.xlsx
+++ b/config/lines/撒粉复合机.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11775" activeTab="3"/>
+    <workbookView windowWidth="28800" windowHeight="11775"/>
   </bookViews>
   <sheets>
     <sheet name="配置" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="192">
   <si>
     <t>配置项</t>
   </si>
@@ -129,10 +129,16 @@
     <t>扫描周期毫秒</t>
   </si>
   <si>
+    <t>ScanIntervalMs</t>
+  </si>
+  <si>
+    <t>发布周期毫秒</t>
+  </si>
+  <si>
     <t>60000</t>
   </si>
   <si>
-    <t>ScanIntervalMs</t>
+    <t>PublishIntervalMs</t>
   </si>
   <si>
     <t>温度发布阈值</t>
@@ -391,6 +397,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>上压辊</t>
     </r>
     <r>
@@ -423,6 +435,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>下压辊</t>
     </r>
     <r>
@@ -548,6 +566,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
       <t>上压辊</t>
     </r>
     <r>
@@ -697,7 +721,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -715,6 +739,12 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1172,155 +1202,156 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
-    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1881,7 +1912,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="14.4285714285714" customWidth="1"/>
@@ -2003,30 +2034,30 @@
       <c r="A11" t="s">
         <v>29</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11">
+        <v>2000</v>
+      </c>
+      <c r="C11" t="s">
         <v>30</v>
       </c>
-      <c r="C11" t="s">
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" s="3" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="12" spans="1:3">
-      <c r="A12" t="s">
+      <c r="B12" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B12" t="s">
+      <c r="C12" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="C12" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
+        <v>34</v>
+      </c>
+      <c r="B13" t="s">
         <v>35</v>
-      </c>
-      <c r="B13" t="s">
-        <v>24</v>
       </c>
       <c r="C13" t="s">
         <v>36</v>
@@ -2036,74 +2067,74 @@
       <c r="A14" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" t="s">
+        <v>24</v>
+      </c>
+      <c r="C14" t="s">
         <v>38</v>
-      </c>
-      <c r="C14" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B15" t="s">
+      <c r="C15" t="s">
         <v>41</v>
-      </c>
-      <c r="C15" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
+        <v>42</v>
+      </c>
+      <c r="B16" t="s">
         <v>43</v>
       </c>
-      <c r="B16" t="s">
+      <c r="C16" t="s">
         <v>44</v>
-      </c>
-      <c r="C16" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:3">
       <c r="A17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B17" t="s">
         <v>46</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>47</v>
-      </c>
-      <c r="C17" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" t="s">
         <v>49</v>
       </c>
-      <c r="B18" t="s">
+      <c r="C18" t="s">
         <v>50</v>
-      </c>
-      <c r="C18" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="19" spans="1:3">
       <c r="A19" t="s">
+        <v>51</v>
+      </c>
+      <c r="B19" t="s">
         <v>52</v>
       </c>
-      <c r="B19" t="s">
+      <c r="C19" t="s">
         <v>53</v>
-      </c>
-      <c r="C19" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="20" spans="1:3">
       <c r="A20" t="s">
+        <v>54</v>
+      </c>
+      <c r="B20" t="s">
         <v>55</v>
-      </c>
-      <c r="B20" t="s">
-        <v>38</v>
       </c>
       <c r="C20" t="s">
         <v>56</v>
@@ -2114,7 +2145,7 @@
         <v>57</v>
       </c>
       <c r="B21" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C21" t="s">
         <v>58</v>
@@ -2125,51 +2156,51 @@
         <v>59</v>
       </c>
       <c r="B22" t="s">
+        <v>35</v>
+      </c>
+      <c r="C22" t="s">
         <v>60</v>
-      </c>
-      <c r="C22" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="23" spans="1:3">
       <c r="A23" t="s">
+        <v>61</v>
+      </c>
+      <c r="B23" t="s">
         <v>62</v>
       </c>
-      <c r="B23" t="s">
+      <c r="C23" t="s">
         <v>63</v>
-      </c>
-      <c r="C23" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="24" spans="1:3">
       <c r="A24" t="s">
+        <v>64</v>
+      </c>
+      <c r="B24" t="s">
         <v>65</v>
       </c>
-      <c r="B24" t="s">
+      <c r="C24" t="s">
         <v>66</v>
-      </c>
-      <c r="C24" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="25" spans="1:3">
       <c r="A25" t="s">
+        <v>67</v>
+      </c>
+      <c r="B25" t="s">
         <v>68</v>
       </c>
-      <c r="B25" t="s">
+      <c r="C25" t="s">
         <v>69</v>
-      </c>
-      <c r="C25" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:3">
       <c r="A26" t="s">
+        <v>70</v>
+      </c>
+      <c r="B26" t="s">
         <v>71</v>
-      </c>
-      <c r="B26" t="s">
-        <v>69</v>
       </c>
       <c r="C26" t="s">
         <v>72</v>
@@ -2180,7 +2211,7 @@
         <v>73</v>
       </c>
       <c r="B27" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C27" t="s">
         <v>74</v>
@@ -2190,11 +2221,22 @@
       <c r="A28" t="s">
         <v>75</v>
       </c>
-      <c r="B28">
-        <v>1</v>
+      <c r="B28" t="s">
+        <v>71</v>
       </c>
       <c r="C28" t="s">
         <v>76</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>77</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+      <c r="C29" t="s">
+        <v>78</v>
       </c>
     </row>
   </sheetData>
@@ -2228,101 +2270,101 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="B7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C7" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C10" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
   </sheetData>
@@ -2344,122 +2386,122 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="B8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="B9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="B11" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="B13" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B14" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B15" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -2489,72 +2531,72 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:13">
       <c r="A1" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J2">
         <v>1</v>
@@ -2563,39 +2605,39 @@
         <v>0</v>
       </c>
       <c r="L2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="M2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="B3" t="s">
+        <v>147</v>
+      </c>
+      <c r="C3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F3" t="s">
         <v>145</v>
       </c>
-      <c r="C3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D3" t="s">
-        <v>146</v>
-      </c>
-      <c r="E3" t="s">
-        <v>83</v>
-      </c>
-      <c r="F3" t="s">
-        <v>143</v>
-      </c>
       <c r="G3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J3">
         <v>1</v>
@@ -2604,39 +2646,39 @@
         <v>0</v>
       </c>
       <c r="L3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="M3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D4" t="s">
+        <v>150</v>
+      </c>
+      <c r="E4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F4" t="s">
         <v>145</v>
       </c>
-      <c r="C4" t="s">
-        <v>83</v>
-      </c>
-      <c r="D4" t="s">
-        <v>148</v>
-      </c>
-      <c r="E4" t="s">
-        <v>83</v>
-      </c>
-      <c r="F4" t="s">
-        <v>143</v>
-      </c>
       <c r="G4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I4" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J4">
         <v>1</v>
@@ -2645,39 +2687,39 @@
         <v>0</v>
       </c>
       <c r="L4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="M4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B5" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C5" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="D5" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E5" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F5" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G5" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I5" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J5">
         <v>1</v>
@@ -2686,39 +2728,39 @@
         <v>0</v>
       </c>
       <c r="L5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B6" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C6" t="s">
+        <v>154</v>
+      </c>
+      <c r="D6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E6" t="s">
         <v>152</v>
       </c>
-      <c r="D6" t="s">
-        <v>148</v>
-      </c>
-      <c r="E6" t="s">
-        <v>150</v>
-      </c>
       <c r="F6" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J6">
         <v>1</v>
@@ -2727,39 +2769,39 @@
         <v>0</v>
       </c>
       <c r="L6" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B7" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C7" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="D7" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E7" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F7" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G7" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I7" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J7">
         <v>1</v>
@@ -2768,39 +2810,39 @@
         <v>0</v>
       </c>
       <c r="L7" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="M7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B8" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C8" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D8" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F8" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I8" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J8">
         <v>1</v>
@@ -2809,39 +2851,39 @@
         <v>0</v>
       </c>
       <c r="L8" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="M8" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C9" t="s">
+        <v>159</v>
+      </c>
+      <c r="D9" t="s">
+        <v>150</v>
+      </c>
+      <c r="E9" t="s">
+        <v>85</v>
+      </c>
+      <c r="F9" t="s">
         <v>145</v>
       </c>
-      <c r="C9" t="s">
-        <v>157</v>
-      </c>
-      <c r="D9" t="s">
-        <v>148</v>
-      </c>
-      <c r="E9" t="s">
-        <v>83</v>
-      </c>
-      <c r="F9" t="s">
-        <v>143</v>
-      </c>
       <c r="G9" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J9">
         <v>1</v>
@@ -2850,39 +2892,39 @@
         <v>0</v>
       </c>
       <c r="L9" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="M9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C10" t="s">
+        <v>160</v>
+      </c>
+      <c r="D10" t="s">
+        <v>150</v>
+      </c>
+      <c r="E10" t="s">
+        <v>85</v>
+      </c>
+      <c r="F10" t="s">
         <v>145</v>
       </c>
-      <c r="C10" t="s">
-        <v>158</v>
-      </c>
-      <c r="D10" t="s">
-        <v>148</v>
-      </c>
-      <c r="E10" t="s">
-        <v>83</v>
-      </c>
-      <c r="F10" t="s">
-        <v>143</v>
-      </c>
       <c r="G10" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I10" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J10">
         <v>1</v>
@@ -2891,39 +2933,39 @@
         <v>0</v>
       </c>
       <c r="L10" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="M10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C11" t="s">
+        <v>85</v>
+      </c>
+      <c r="D11" t="s">
+        <v>150</v>
+      </c>
+      <c r="E11" t="s">
+        <v>85</v>
+      </c>
+      <c r="F11" t="s">
         <v>145</v>
       </c>
-      <c r="C11" t="s">
-        <v>83</v>
-      </c>
-      <c r="D11" t="s">
-        <v>148</v>
-      </c>
-      <c r="E11" t="s">
-        <v>83</v>
-      </c>
-      <c r="F11" t="s">
-        <v>143</v>
-      </c>
       <c r="G11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J11">
         <v>1</v>
@@ -2932,39 +2974,39 @@
         <v>0</v>
       </c>
       <c r="L11" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="M11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="B12" t="s">
+        <v>147</v>
+      </c>
+      <c r="C12" t="s">
+        <v>85</v>
+      </c>
+      <c r="D12" t="s">
+        <v>150</v>
+      </c>
+      <c r="E12" t="s">
+        <v>85</v>
+      </c>
+      <c r="F12" t="s">
         <v>145</v>
       </c>
-      <c r="C12" t="s">
-        <v>83</v>
-      </c>
-      <c r="D12" t="s">
-        <v>148</v>
-      </c>
-      <c r="E12" t="s">
-        <v>83</v>
-      </c>
-      <c r="F12" t="s">
-        <v>143</v>
-      </c>
       <c r="G12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I12" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J12">
         <v>1</v>
@@ -2973,39 +3015,39 @@
         <v>0</v>
       </c>
       <c r="L12" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="M12" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C13" t="s">
+        <v>85</v>
+      </c>
+      <c r="D13" t="s">
+        <v>150</v>
+      </c>
+      <c r="E13" t="s">
+        <v>85</v>
+      </c>
+      <c r="F13" t="s">
         <v>145</v>
       </c>
-      <c r="C13" t="s">
-        <v>83</v>
-      </c>
-      <c r="D13" t="s">
-        <v>148</v>
-      </c>
-      <c r="E13" t="s">
-        <v>83</v>
-      </c>
-      <c r="F13" t="s">
-        <v>143</v>
-      </c>
       <c r="G13" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I13" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J13">
         <v>1</v>
@@ -3014,39 +3056,39 @@
         <v>0</v>
       </c>
       <c r="L13" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="M13" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C14" t="s">
+        <v>85</v>
+      </c>
+      <c r="D14" t="s">
+        <v>150</v>
+      </c>
+      <c r="E14" t="s">
+        <v>85</v>
+      </c>
+      <c r="F14" t="s">
         <v>145</v>
       </c>
-      <c r="C14" t="s">
-        <v>83</v>
-      </c>
-      <c r="D14" t="s">
-        <v>148</v>
-      </c>
-      <c r="E14" t="s">
-        <v>83</v>
-      </c>
-      <c r="F14" t="s">
-        <v>143</v>
-      </c>
       <c r="G14" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H14" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I14" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J14">
         <v>1</v>
@@ -3055,39 +3097,39 @@
         <v>0</v>
       </c>
       <c r="L14" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="M14" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C15" t="s">
+        <v>85</v>
+      </c>
+      <c r="D15" t="s">
+        <v>150</v>
+      </c>
+      <c r="E15" t="s">
+        <v>85</v>
+      </c>
+      <c r="F15" t="s">
         <v>145</v>
       </c>
-      <c r="C15" t="s">
-        <v>83</v>
-      </c>
-      <c r="D15" t="s">
-        <v>148</v>
-      </c>
-      <c r="E15" t="s">
-        <v>83</v>
-      </c>
-      <c r="F15" t="s">
-        <v>143</v>
-      </c>
       <c r="G15" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I15" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="J15">
         <v>1</v>
@@ -3096,10 +3138,10 @@
         <v>0</v>
       </c>
       <c r="L15" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="M15" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -3123,96 +3165,96 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="D3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B4" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C4" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D4" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="B5" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C5" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D5" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B6" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="D6" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -3242,72 +3284,72 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:11">
       <c r="A1" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D2">
         <v>1888</v>
       </c>
       <c r="E2" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
       <c r="J2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>

--- a/config/lines/撒粉复合机.xlsx
+++ b/config/lines/撒粉复合机.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11775"/>
+    <workbookView windowWidth="28800" windowHeight="11775" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="配置" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="192">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="183">
   <si>
     <t>配置项</t>
   </si>
@@ -385,12 +385,6 @@
   </si>
   <si>
     <t>主辊筒车速</t>
-  </si>
-  <si>
-    <t>syg1</t>
-  </si>
-  <si>
-    <t>上压辊1（闭合/打开）</t>
   </si>
   <si>
     <t>syg1jx</t>
@@ -425,44 +419,6 @@
     </r>
   </si>
   <si>
-    <t>xyg2</t>
-  </si>
-  <si>
-    <t>下压辊2（闭合/打开）</t>
-  </si>
-  <si>
-    <t>xyg2jx</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>下压辊</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>间隙</t>
-    </r>
-  </si>
-  <si>
     <t>qdjj</t>
   </si>
   <si>
@@ -563,59 +519,6 @@
   </si>
   <si>
     <t>工艺参数</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>上压辊</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（闭合</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <charset val="134"/>
-      </rPr>
-      <t>/</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="宋体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>打开）</t>
-    </r>
-  </si>
-  <si>
-    <t>D1040</t>
-  </si>
-  <si>
-    <t>D1060</t>
   </si>
   <si>
     <t>主题色</t>
@@ -721,7 +624,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -739,12 +642,6 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1202,148 +1099,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1351,7 +1248,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2377,7 +2274,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="10.5714285714286" customWidth="1"/>
@@ -2452,7 +2349,7 @@
       <c r="A9" t="s">
         <v>116</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="2" t="s">
         <v>117</v>
       </c>
     </row>
@@ -2460,7 +2357,7 @@
       <c r="A10" t="s">
         <v>118</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" t="s">
         <v>119</v>
       </c>
     </row>
@@ -2476,32 +2373,8 @@
       <c r="A12" t="s">
         <v>122</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" t="s">
         <v>123</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" t="s">
-        <v>124</v>
-      </c>
-      <c r="B13" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" t="s">
-        <v>126</v>
-      </c>
-      <c r="B14" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" t="s">
-        <v>128</v>
-      </c>
-      <c r="B15" t="s">
-        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -2514,7 +2387,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="46.7142857142857" customWidth="1"/>
@@ -2531,43 +2404,43 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:13">
       <c r="A1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>137</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>37</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>138</v>
+        <v>132</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>141</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -2575,19 +2448,19 @@
         <v>103</v>
       </c>
       <c r="B2" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C2" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="D2" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="E2" t="s">
         <v>85</v>
       </c>
       <c r="F2" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="G2" t="s">
         <v>71</v>
@@ -2605,7 +2478,7 @@
         <v>0</v>
       </c>
       <c r="L2" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="M2" t="s">
         <v>40</v>
@@ -2616,19 +2489,19 @@
         <v>105</v>
       </c>
       <c r="B3" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C3" t="s">
         <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="E3" t="s">
         <v>85</v>
       </c>
       <c r="F3" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="G3" t="s">
         <v>71</v>
@@ -2646,7 +2519,7 @@
         <v>0</v>
       </c>
       <c r="L3" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="M3" t="s">
         <v>40</v>
@@ -2657,19 +2530,19 @@
         <v>107</v>
       </c>
       <c r="B4" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C4" t="s">
         <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="E4" t="s">
         <v>85</v>
       </c>
       <c r="F4" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="G4" t="s">
         <v>71</v>
@@ -2687,7 +2560,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="M4" t="s">
         <v>40</v>
@@ -2698,19 +2571,19 @@
         <v>109</v>
       </c>
       <c r="B5" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C5" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="D5" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="E5" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="F5" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="G5" t="s">
         <v>71</v>
@@ -2728,7 +2601,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="M5" t="s">
         <v>40</v>
@@ -2739,19 +2612,19 @@
         <v>111</v>
       </c>
       <c r="B6" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C6" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="D6" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="E6" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="F6" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="G6" t="s">
         <v>71</v>
@@ -2769,7 +2642,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="M6" t="s">
         <v>40</v>
@@ -2780,19 +2653,19 @@
         <v>113</v>
       </c>
       <c r="B7" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C7" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="D7" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="E7" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="F7" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="G7" t="s">
         <v>71</v>
@@ -2810,7 +2683,7 @@
         <v>0</v>
       </c>
       <c r="L7" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="M7" t="s">
         <v>40</v>
@@ -2821,19 +2694,19 @@
         <v>115</v>
       </c>
       <c r="B8" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="C8" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="D8" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="E8" t="s">
         <v>85</v>
       </c>
       <c r="F8" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="G8" t="s">
         <v>71</v>
@@ -2851,30 +2724,30 @@
         <v>0</v>
       </c>
       <c r="L8" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="M8" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" s="2" t="s">
-        <v>158</v>
+      <c r="A9" t="s">
+        <v>119</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C9" t="s">
-        <v>159</v>
+        <v>85</v>
       </c>
       <c r="D9" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="E9" t="s">
         <v>85</v>
       </c>
       <c r="F9" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="G9" t="s">
         <v>71</v>
@@ -2892,7 +2765,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="M9" t="s">
         <v>40</v>
@@ -2902,20 +2775,20 @@
       <c r="A10" t="s">
         <v>121</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>147</v>
+      <c r="B10" t="s">
+        <v>141</v>
       </c>
       <c r="C10" t="s">
-        <v>160</v>
+        <v>85</v>
       </c>
       <c r="D10" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="E10" t="s">
         <v>85</v>
       </c>
       <c r="F10" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="G10" t="s">
         <v>71</v>
@@ -2933,7 +2806,7 @@
         <v>0</v>
       </c>
       <c r="L10" t="s">
-        <v>157</v>
+        <v>143</v>
       </c>
       <c r="M10" t="s">
         <v>40</v>
@@ -2941,22 +2814,22 @@
     </row>
     <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C11" t="s">
         <v>85</v>
       </c>
       <c r="D11" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="E11" t="s">
         <v>85</v>
       </c>
       <c r="F11" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="G11" t="s">
         <v>71</v>
@@ -2974,30 +2847,30 @@
         <v>0</v>
       </c>
       <c r="L11" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="M11" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" t="s">
-        <v>127</v>
-      </c>
-      <c r="B12" t="s">
-        <v>147</v>
+      <c r="A12" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>141</v>
       </c>
       <c r="C12" t="s">
         <v>85</v>
       </c>
       <c r="D12" t="s">
-        <v>150</v>
+        <v>144</v>
       </c>
       <c r="E12" t="s">
         <v>85</v>
       </c>
       <c r="F12" t="s">
-        <v>145</v>
+        <v>139</v>
       </c>
       <c r="G12" t="s">
         <v>71</v>
@@ -3015,132 +2888,9 @@
         <v>0</v>
       </c>
       <c r="L12" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="M12" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
-      <c r="A13" t="s">
-        <v>129</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C13" t="s">
-        <v>85</v>
-      </c>
-      <c r="D13" t="s">
-        <v>150</v>
-      </c>
-      <c r="E13" t="s">
-        <v>85</v>
-      </c>
-      <c r="F13" t="s">
-        <v>145</v>
-      </c>
-      <c r="G13" t="s">
-        <v>71</v>
-      </c>
-      <c r="H13" t="s">
-        <v>85</v>
-      </c>
-      <c r="I13" t="s">
-        <v>85</v>
-      </c>
-      <c r="J13">
-        <v>1</v>
-      </c>
-      <c r="K13">
-        <v>0</v>
-      </c>
-      <c r="L13" t="s">
-        <v>149</v>
-      </c>
-      <c r="M13" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
-      <c r="A14" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C14" t="s">
-        <v>85</v>
-      </c>
-      <c r="D14" t="s">
-        <v>150</v>
-      </c>
-      <c r="E14" t="s">
-        <v>85</v>
-      </c>
-      <c r="F14" t="s">
-        <v>145</v>
-      </c>
-      <c r="G14" t="s">
-        <v>71</v>
-      </c>
-      <c r="H14" t="s">
-        <v>85</v>
-      </c>
-      <c r="I14" t="s">
-        <v>85</v>
-      </c>
-      <c r="J14">
-        <v>1</v>
-      </c>
-      <c r="K14">
-        <v>0</v>
-      </c>
-      <c r="L14" t="s">
-        <v>149</v>
-      </c>
-      <c r="M14" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
-      <c r="A15" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C15" t="s">
-        <v>85</v>
-      </c>
-      <c r="D15" t="s">
-        <v>150</v>
-      </c>
-      <c r="E15" t="s">
-        <v>85</v>
-      </c>
-      <c r="F15" t="s">
-        <v>145</v>
-      </c>
-      <c r="G15" t="s">
-        <v>71</v>
-      </c>
-      <c r="H15" t="s">
-        <v>85</v>
-      </c>
-      <c r="I15" t="s">
-        <v>85</v>
-      </c>
-      <c r="J15">
-        <v>1</v>
-      </c>
-      <c r="K15">
-        <v>0</v>
-      </c>
-      <c r="L15" t="s">
-        <v>149</v>
-      </c>
-      <c r="M15" t="s">
         <v>40</v>
       </c>
     </row>
@@ -3165,96 +2915,96 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:4">
       <c r="A1" s="1" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>161</v>
+        <v>152</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>162</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2" t="s">
-        <v>146</v>
+        <v>140</v>
       </c>
       <c r="B2" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="C2" t="s">
-        <v>164</v>
+        <v>155</v>
       </c>
       <c r="D2" t="s">
-        <v>165</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" t="s">
-        <v>153</v>
+        <v>147</v>
       </c>
       <c r="B3" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="C3" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="D3" t="s">
-        <v>168</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="B4" t="s">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="C4" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="D4" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="B5" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="C5" t="s">
-        <v>173</v>
+        <v>164</v>
       </c>
       <c r="D5" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="B6" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="C6" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="D6" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -3284,42 +3034,42 @@
   <sheetData>
     <row r="1" s="1" customFormat="1" spans="1:11">
       <c r="A1" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>136</v>
-      </c>
       <c r="C1" s="1" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="B2" t="s">
         <v>71</v>
@@ -3349,7 +3099,7 @@
         <v>62</v>
       </c>
       <c r="K2" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
     </row>
   </sheetData>

--- a/config/lines/撒粉复合机.xlsx
+++ b/config/lines/撒粉复合机.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="11775" activeTab="3"/>
+    <workbookView windowWidth="23040" windowHeight="12360" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="配置" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="184">
   <si>
     <t>配置项</t>
   </si>
@@ -519,6 +519,9 @@
   </si>
   <si>
     <t>工艺参数</t>
+  </si>
+  <si>
+    <t>D1050</t>
   </si>
   <si>
     <t>主题色</t>
@@ -2858,10 +2861,10 @@
         <v>117</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>152</v>
       </c>
       <c r="D12" t="s">
         <v>144</v>
@@ -2921,10 +2924,10 @@
         <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -2932,13 +2935,13 @@
         <v>140</v>
       </c>
       <c r="B2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -2946,13 +2949,13 @@
         <v>147</v>
       </c>
       <c r="B3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -2960,13 +2963,13 @@
         <v>151</v>
       </c>
       <c r="B4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -2974,37 +2977,37 @@
         <v>143</v>
       </c>
       <c r="B5" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C5" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D5" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="D6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -3040,36 +3043,36 @@
         <v>130</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B2" t="s">
         <v>71</v>
@@ -3099,7 +3102,7 @@
         <v>62</v>
       </c>
       <c r="K2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
